--- a/artfynd/A 29150-2023 artfynd.xlsx
+++ b/artfynd/A 29150-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,52 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>108893088</v>
+        <v>135470915</v>
       </c>
       <c r="B2" t="n">
-        <v>4711</v>
+        <v>91974</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100813</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Urskogsänger</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dermestes palmi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sjöberg, 1950</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kloken, Nb</t>
+          <t>Vitvattenstjärnen, Vitvattenstjärnen, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>762736</v>
+        <v>762873</v>
       </c>
       <c r="R2" t="n">
-        <v>7357792</v>
+        <v>7357987</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -744,17 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-06-07</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-06-07</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Leg. Sveaskog, inventering Klokenlandskapet</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,88 +756,64 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>asphögstubbe</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>Sven Lennartsson</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>SL06158</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>Sven Lennartsson</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Joel Hallqvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Joel Hallqvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>108893078</v>
+        <v>135472071</v>
       </c>
       <c r="B3" t="n">
-        <v>7202</v>
+        <v>92539</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102355</v>
+        <v>2046</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Björkplattnos</t>
+          <t>Vit aspticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Gonotropis dorsalis</t>
+          <t>Favolus pseudobetulinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Thunberg, 1796)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Murashk. ex Pilát) Sotome &amp; T.Hatt.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kloken, Nb</t>
+          <t>Lillholmstjärnen, Lillholmstjärnen, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>762736</v>
+        <v>762716</v>
       </c>
       <c r="R3" t="n">
-        <v>7357792</v>
+        <v>7357784</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,17 +837,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-06-07</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-06-07</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Leg. Sveaskog, inventering Klokenlandskapet</t>
+          <t>Sannolikt vit aspticka, ca 5 meter upp på gammal asp.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,92 +858,68 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>björkhögstubbe</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>Sven Lennartsson</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>SL06155</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>Sven Lennartsson</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Joel Hallqvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Joel Hallqvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126096586</v>
+        <v>108893088</v>
       </c>
       <c r="B4" t="n">
-        <v>98050</v>
+        <v>4711</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222112</v>
+        <v>100813</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Månlåsbräken</t>
+          <t>Urskogsänger</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Botrychium lunaria</t>
+          <t>Dermestes palmi</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Sw.</t>
+          <t>Sjöberg, 1950</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lilledal, Edefors, Nb</t>
+          <t>Kloken, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>763114</v>
+        <v>762736</v>
       </c>
       <c r="R4" t="n">
-        <v>7357849</v>
+        <v>7357792</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1000,27 +943,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>14:15</t>
+          <t>2020-06-07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>14:15</t>
+          <t>2020-06-07</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På en gammal odling.</t>
+          <t>Leg. Sveaskog, inventering Klokenlandskapet</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,22 +962,1452 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>asphögstubbe</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>Sven Lennartsson</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>SL06158</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>Sven Lennartsson</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Joel Hallqvist</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Via Joel Hallqvist</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>108893078</v>
+      </c>
+      <c r="B5" t="n">
+        <v>7202</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>102355</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Björkplattnos</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Gonotropis dorsalis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Thunberg, 1796)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Kloken, Nb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>762736</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7357792</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2020-06-07</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2020-06-07</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Leg. Sveaskog, inventering Klokenlandskapet</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>björkhögstubbe</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>Sven Lennartsson</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>SL06155</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>Sven Lennartsson</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Joel Hallqvist</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Via Joel Hallqvist</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135471096</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98219</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>219815</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ekbräken</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Gymnocarpium dryopteris</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Newman</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Vitvattenstjärnen, Vitvattenstjärnen, Nb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>763034</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7357951</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135471008</v>
+      </c>
+      <c r="B7" t="n">
+        <v>108205</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220083</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Brudborste</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Cirsium heterophyllum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Vitvattenstjärnen, Vitvattenstjärnen, Nb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>762971</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7357996</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135471045</v>
+      </c>
+      <c r="B8" t="n">
+        <v>111153</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Vitvattenstjärnen, Vitvattenstjärnen, Nb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>762989</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7357997</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135471383</v>
+      </c>
+      <c r="B9" t="n">
+        <v>111153</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Vitvattenstjärnen, Vitvattenstjärnen, Nb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>763029</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7357880</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135470767</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Vitvattenstjärnen, Vitvattenstjärnen, Nb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>762791</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7357976</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135470842</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Vitvattenstjärnen, Vitvattenstjärnen, Nb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>762818</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7357982</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135470894</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Vitvattenstjärnen, Vitvattenstjärnen, Nb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>762849</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7357984</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135471196</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Vitvattenstjärnen, Vitvattenstjärnen, Nb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>763055</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7357920</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135471252</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Vitvattenstjärnen, Vitvattenstjärnen, Nb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>763062</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7357921</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135471308</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Vitvattenstjärnen, Vitvattenstjärnen, Nb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>763045</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7357902</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135470858</v>
+      </c>
+      <c r="B16" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Vitvattenstjärnen, Vitvattenstjärnen, Nb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>762850</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7357989</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135471400</v>
+      </c>
+      <c r="B17" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Vitvattenstjärnen, Vitvattenstjärnen, Nb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>763030</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7357880</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>126096586</v>
+      </c>
+      <c r="B18" t="n">
+        <v>98050</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>222112</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Månlåsbräken</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Botrychium lunaria</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Sw.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Lilledal, Edefors, Nb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>763114</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7357849</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På en gammal odling.</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
           <t>Mats Bergquist</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX18" t="inlineStr">
         <is>
           <t>Mats Bergquist</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29150-2023 artfynd.xlsx
+++ b/artfynd/A 29150-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1126,48 +1126,53 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135471096</v>
+        <v>135483668</v>
       </c>
       <c r="B6" t="n">
-        <v>98219</v>
+        <v>58136</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219815</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ekbräken</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Gymnocarpium dryopteris</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Newman</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Vitvattenstjärnen, Vitvattenstjärnen, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>763034</v>
+        <v>763047</v>
       </c>
       <c r="R6" t="n">
-        <v>7357951</v>
+        <v>7357847</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1191,12 +1196,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,10 +1228,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135471008</v>
+        <v>135471096</v>
       </c>
       <c r="B7" t="n">
-        <v>108205</v>
+        <v>98219</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1234,21 +1239,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220083</v>
+        <v>219815</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Ekbräken</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Gymnocarpium dryopteris</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(L.) Newman</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1258,10 +1263,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>762971</v>
+        <v>763034</v>
       </c>
       <c r="R7" t="n">
-        <v>7357996</v>
+        <v>7357951</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1320,10 +1325,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135471045</v>
+        <v>135471008</v>
       </c>
       <c r="B8" t="n">
-        <v>111153</v>
+        <v>108205</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1331,21 +1336,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220240</v>
+        <v>220083</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1355,10 +1360,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>762989</v>
+        <v>762971</v>
       </c>
       <c r="R8" t="n">
-        <v>7357997</v>
+        <v>7357996</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,7 +1422,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135471383</v>
+        <v>135471045</v>
       </c>
       <c r="B9" t="n">
         <v>111153</v>
@@ -1452,10 +1457,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>763029</v>
+        <v>762989</v>
       </c>
       <c r="R9" t="n">
-        <v>7357880</v>
+        <v>7357997</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1514,32 +1519,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135470767</v>
+        <v>135471383</v>
       </c>
       <c r="B10" t="n">
-        <v>99195</v>
+        <v>111153</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>220240</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1549,10 +1554,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>762791</v>
+        <v>763029</v>
       </c>
       <c r="R10" t="n">
-        <v>7357976</v>
+        <v>7357880</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1611,7 +1616,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135470842</v>
+        <v>135470767</v>
       </c>
       <c r="B11" t="n">
         <v>99195</v>
@@ -1646,10 +1651,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>762818</v>
+        <v>762791</v>
       </c>
       <c r="R11" t="n">
-        <v>7357982</v>
+        <v>7357976</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,7 +1713,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135470894</v>
+        <v>135470842</v>
       </c>
       <c r="B12" t="n">
         <v>99195</v>
@@ -1743,10 +1748,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>762849</v>
+        <v>762818</v>
       </c>
       <c r="R12" t="n">
-        <v>7357984</v>
+        <v>7357982</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1805,7 +1810,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135471196</v>
+        <v>135470894</v>
       </c>
       <c r="B13" t="n">
         <v>99195</v>
@@ -1840,10 +1845,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>763055</v>
+        <v>762849</v>
       </c>
       <c r="R13" t="n">
-        <v>7357920</v>
+        <v>7357984</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1902,7 +1907,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135471252</v>
+        <v>135471196</v>
       </c>
       <c r="B14" t="n">
         <v>99195</v>
@@ -1937,10 +1942,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>763062</v>
+        <v>763055</v>
       </c>
       <c r="R14" t="n">
-        <v>7357921</v>
+        <v>7357920</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1999,7 +2004,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135471308</v>
+        <v>135471252</v>
       </c>
       <c r="B15" t="n">
         <v>99195</v>
@@ -2034,10 +2039,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>763045</v>
+        <v>763062</v>
       </c>
       <c r="R15" t="n">
-        <v>7357902</v>
+        <v>7357921</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2096,32 +2101,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135470858</v>
+        <v>135471308</v>
       </c>
       <c r="B16" t="n">
-        <v>98060</v>
+        <v>99195</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2131,10 +2136,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>762850</v>
+        <v>763045</v>
       </c>
       <c r="R16" t="n">
-        <v>7357989</v>
+        <v>7357902</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2193,7 +2198,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135471400</v>
+        <v>135470858</v>
       </c>
       <c r="B17" t="n">
         <v>98060</v>
@@ -2228,10 +2233,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>763030</v>
+        <v>762850</v>
       </c>
       <c r="R17" t="n">
-        <v>7357880</v>
+        <v>7357989</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2290,53 +2295,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126096586</v>
+        <v>135471400</v>
       </c>
       <c r="B18" t="n">
-        <v>98050</v>
+        <v>98060</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222112</v>
+        <v>221945</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Månlåsbräken</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Botrychium lunaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Sw.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lilledal, Edefors, Nb</t>
+          <t>Vitvattenstjärnen, Vitvattenstjärnen, Nb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>763114</v>
+        <v>763030</v>
       </c>
       <c r="R18" t="n">
-        <v>7357849</v>
+        <v>7357880</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2363,27 +2360,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>14:15</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På en gammal odling.</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2392,22 +2374,142 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>126096586</v>
+      </c>
+      <c r="B19" t="n">
+        <v>98050</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>222112</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Månlåsbräken</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Botrychium lunaria</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) Sw.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Lilledal, Edefors, Nb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>763114</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7357849</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På en gammal odling.</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
           <t>Mats Bergquist</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
+      <c r="AX19" t="inlineStr">
         <is>
           <t>Mats Bergquist</t>
         </is>
       </c>
-      <c r="AY18" t="inlineStr"/>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29150-2023 artfynd.xlsx
+++ b/artfynd/A 29150-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135470915</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135472071</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -997,6 +1012,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108893088</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1123,6 +1143,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108893078</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1225,6 +1250,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135483668</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1322,6 +1352,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135471096</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1419,6 +1454,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135471008</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1516,6 +1556,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135471045</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1613,6 +1658,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135471383</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1710,6 +1760,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135470767</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1807,6 +1862,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135470842</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1904,6 +1964,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135470894</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2001,6 +2066,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135471196</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2098,6 +2168,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135471252</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2195,6 +2270,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135471308</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2292,6 +2372,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135470858</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2389,6 +2474,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135471400</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2510,8 +2600,33 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126096586</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 29150-2023 artfynd.xlsx
+++ b/artfynd/A 29150-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135470915</v>
       </c>
       <c r="B2" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135472071</v>
       </c>
       <c r="B3" t="n">
-        <v>92539</v>
+        <v>92581</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>135483668</v>
       </c>
       <c r="B6" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>135471096</v>
       </c>
       <c r="B7" t="n">
-        <v>98219</v>
+        <v>98263</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>135471008</v>
       </c>
       <c r="B8" t="n">
-        <v>108205</v>
+        <v>108260</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>135471045</v>
       </c>
       <c r="B9" t="n">
-        <v>111153</v>
+        <v>111210</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1567,7 +1567,7 @@
         <v>135471383</v>
       </c>
       <c r="B10" t="n">
-        <v>111153</v>
+        <v>111210</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>135470767</v>
       </c>
       <c r="B11" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>135470842</v>
       </c>
       <c r="B12" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>135470894</v>
       </c>
       <c r="B13" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>135471196</v>
       </c>
       <c r="B14" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>135471252</v>
       </c>
       <c r="B15" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2179,7 +2179,7 @@
         <v>135471308</v>
       </c>
       <c r="B16" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         <v>135470858</v>
       </c>
       <c r="B17" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>135471400</v>
       </c>
       <c r="B18" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 29150-2023 artfynd.xlsx
+++ b/artfynd/A 29150-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135470915</v>
       </c>
       <c r="B2" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135472071</v>
       </c>
       <c r="B3" t="n">
-        <v>92581</v>
+        <v>92608</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>135471096</v>
       </c>
       <c r="B7" t="n">
-        <v>98263</v>
+        <v>98290</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>135471008</v>
       </c>
       <c r="B8" t="n">
-        <v>108260</v>
+        <v>108287</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>135471045</v>
       </c>
       <c r="B9" t="n">
-        <v>111210</v>
+        <v>111237</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1567,7 +1567,7 @@
         <v>135471383</v>
       </c>
       <c r="B10" t="n">
-        <v>111210</v>
+        <v>111237</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>135470767</v>
       </c>
       <c r="B11" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>135470842</v>
       </c>
       <c r="B12" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>135470894</v>
       </c>
       <c r="B13" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>135471196</v>
       </c>
       <c r="B14" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>135471252</v>
       </c>
       <c r="B15" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2179,7 +2179,7 @@
         <v>135471308</v>
       </c>
       <c r="B16" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         <v>135470858</v>
       </c>
       <c r="B17" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>135471400</v>
       </c>
       <c r="B18" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 29150-2023 artfynd.xlsx
+++ b/artfynd/A 29150-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,52 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>108893088</v>
+        <v>135470915</v>
       </c>
       <c r="B2" t="n">
-        <v>4711</v>
+        <v>92048</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100813</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Urskogsänger</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dermestes palmi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sjöberg, 1950</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kloken, Nb</t>
+          <t>Vitvattenstjärnen, Vitvattenstjärnen, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>762736</v>
+        <v>762873</v>
       </c>
       <c r="R2" t="n">
-        <v>7357792</v>
+        <v>7357987</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,17 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-06-07</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-06-07</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Leg. Sveaskog, inventering Klokenlandskapet</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,93 +761,69 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>asphögstubbe</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>Sven Lennartsson</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>SL06158</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>Sven Lennartsson</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Joel Hallqvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Joel Hallqvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/108893088</t>
+          <t>https://artportalen.se/Sighting/135470915</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>108893078</v>
+        <v>135472071</v>
       </c>
       <c r="B3" t="n">
-        <v>7202</v>
+        <v>92613</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102355</v>
+        <v>2046</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Björkplattnos</t>
+          <t>Vit aspticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Gonotropis dorsalis</t>
+          <t>Favolus pseudobetulinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Thunberg, 1796)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Murashk. ex Pilát) Sotome &amp; T.Hatt.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kloken, Nb</t>
+          <t>Lillholmstjärnen, Lillholmstjärnen, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>762736</v>
+        <v>762716</v>
       </c>
       <c r="R3" t="n">
-        <v>7357792</v>
+        <v>7357784</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,17 +847,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-06-07</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-06-07</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Leg. Sveaskog, inventering Klokenlandskapet</t>
+          <t>Sannolikt vit aspticka, ca 5 meter upp på gammal asp.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,97 +868,73 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>björkhögstubbe</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>Sven Lennartsson</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>SL06155</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>Sven Lennartsson</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Joel Hallqvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Joel Hallqvist</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/108893078</t>
+          <t>https://artportalen.se/Sighting/135472071</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126096586</v>
+        <v>108893088</v>
       </c>
       <c r="B4" t="n">
-        <v>98050</v>
+        <v>4711</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222112</v>
+        <v>100813</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Månlåsbräken</t>
+          <t>Urskogsänger</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Botrychium lunaria</t>
+          <t>Dermestes palmi</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Sw.</t>
+          <t>Sjöberg, 1950</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lilledal, Edefors, Nb</t>
+          <t>Kloken, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>763114</v>
+        <v>762736</v>
       </c>
       <c r="R4" t="n">
-        <v>7357849</v>
+        <v>7357792</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1015,27 +958,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>14:15</t>
+          <t>2020-06-07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>14:15</t>
+          <t>2020-06-07</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På en gammal odling.</t>
+          <t>Leg. Sveaskog, inventering Klokenlandskapet</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1044,23 +977,1630 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>asphögstubbe</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>Sven Lennartsson</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>SL06158</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>Sven Lennartsson</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Mats Bergquist</t>
+          <t>Joel Hallqvist</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mats Bergquist</t>
+          <t>Via Joel Hallqvist</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108893088</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>108893078</v>
+      </c>
+      <c r="B5" t="n">
+        <v>7202</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>102355</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Björkplattnos</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Gonotropis dorsalis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Thunberg, 1796)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Kloken, Nb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>762736</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7357792</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2020-06-07</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2020-06-07</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Leg. Sveaskog, inventering Klokenlandskapet</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>björkhögstubbe</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>Sven Lennartsson</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>SL06155</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>Sven Lennartsson</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Joel Hallqvist</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Via Joel Hallqvist</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108893078</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135483668</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Vitvattenstjärnen, Vitvattenstjärnen, Nb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>763047</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7357847</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135483668</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135471096</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98295</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>219815</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ekbräken</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Gymnocarpium dryopteris</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Newman</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Vitvattenstjärnen, Vitvattenstjärnen, Nb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>763034</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7357951</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135471096</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135471008</v>
+      </c>
+      <c r="B8" t="n">
+        <v>108292</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220083</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Brudborste</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Cirsium heterophyllum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Vitvattenstjärnen, Vitvattenstjärnen, Nb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>762971</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7357996</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135471008</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135471045</v>
+      </c>
+      <c r="B9" t="n">
+        <v>111242</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Vitvattenstjärnen, Vitvattenstjärnen, Nb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>762989</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7357997</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135471045</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135471383</v>
+      </c>
+      <c r="B10" t="n">
+        <v>111242</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Vitvattenstjärnen, Vitvattenstjärnen, Nb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>763029</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7357880</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135471383</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135470767</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Vitvattenstjärnen, Vitvattenstjärnen, Nb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>762791</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7357976</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135470767</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135470842</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Vitvattenstjärnen, Vitvattenstjärnen, Nb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>762818</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7357982</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135470842</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135470894</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Vitvattenstjärnen, Vitvattenstjärnen, Nb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>762849</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7357984</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135470894</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135471196</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Vitvattenstjärnen, Vitvattenstjärnen, Nb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>763055</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7357920</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135471196</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135471252</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Vitvattenstjärnen, Vitvattenstjärnen, Nb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>763062</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7357921</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135471252</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135471308</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Vitvattenstjärnen, Vitvattenstjärnen, Nb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>763045</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7357902</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135471308</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135470858</v>
+      </c>
+      <c r="B17" t="n">
+        <v>98136</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Vitvattenstjärnen, Vitvattenstjärnen, Nb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>762850</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7357989</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135470858</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135471400</v>
+      </c>
+      <c r="B18" t="n">
+        <v>98136</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Vitvattenstjärnen, Vitvattenstjärnen, Nb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>763030</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7357880</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135471400</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>126096586</v>
+      </c>
+      <c r="B19" t="n">
+        <v>98050</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>222112</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Månlåsbräken</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Botrychium lunaria</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) Sw.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Lilledal, Edefors, Nb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>763114</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7357849</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Edefors</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På en gammal odling.</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Mats Bergquist</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Mats Bergquist</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/126096586</t>
         </is>
@@ -1071,6 +2611,21 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29150-2023 artfynd.xlsx
+++ b/artfynd/A 29150-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135470915</v>
       </c>
       <c r="B2" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135472071</v>
       </c>
       <c r="B3" t="n">
-        <v>92613</v>
+        <v>92615</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>135471096</v>
       </c>
       <c r="B7" t="n">
-        <v>98295</v>
+        <v>98297</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>135471008</v>
       </c>
       <c r="B8" t="n">
-        <v>108292</v>
+        <v>108294</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>135471045</v>
       </c>
       <c r="B9" t="n">
-        <v>111242</v>
+        <v>111244</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1567,7 +1567,7 @@
         <v>135471383</v>
       </c>
       <c r="B10" t="n">
-        <v>111242</v>
+        <v>111244</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>135470767</v>
       </c>
       <c r="B11" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>135470842</v>
       </c>
       <c r="B12" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>135470894</v>
       </c>
       <c r="B13" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>135471196</v>
       </c>
       <c r="B14" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>135471252</v>
       </c>
       <c r="B15" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2179,7 +2179,7 @@
         <v>135471308</v>
       </c>
       <c r="B16" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         <v>135470858</v>
       </c>
       <c r="B17" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>135471400</v>
       </c>
       <c r="B18" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 29150-2023 artfynd.xlsx
+++ b/artfynd/A 29150-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135470915</v>
       </c>
       <c r="B2" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135472071</v>
       </c>
       <c r="B3" t="n">
-        <v>92615</v>
+        <v>92630</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>135483668</v>
       </c>
       <c r="B6" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>135471096</v>
       </c>
       <c r="B7" t="n">
-        <v>98297</v>
+        <v>98314</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>135471008</v>
       </c>
       <c r="B8" t="n">
-        <v>108294</v>
+        <v>108317</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1465,7 +1465,7 @@
         <v>135471045</v>
       </c>
       <c r="B9" t="n">
-        <v>111244</v>
+        <v>111267</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1567,7 +1567,7 @@
         <v>135471383</v>
       </c>
       <c r="B10" t="n">
-        <v>111244</v>
+        <v>111267</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1669,7 +1669,7 @@
         <v>135470767</v>
       </c>
       <c r="B11" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>135470842</v>
       </c>
       <c r="B12" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>135470894</v>
       </c>
       <c r="B13" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         <v>135471196</v>
       </c>
       <c r="B14" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
         <v>135471252</v>
       </c>
       <c r="B15" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2179,7 +2179,7 @@
         <v>135471308</v>
       </c>
       <c r="B16" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         <v>135470858</v>
       </c>
       <c r="B17" t="n">
-        <v>98138</v>
+        <v>98155</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>135471400</v>
       </c>
       <c r="B18" t="n">
-        <v>98138</v>
+        <v>98155</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
